--- a/build/stock_latest.xlsx
+++ b/build/stock_latest.xlsx
@@ -3548,10 +3548,10 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F108" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>7</v>
@@ -13466,10 +13466,10 @@
         <v>28</v>
       </c>
       <c r="E450" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="F450" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G450" t="n">
         <v>148</v>
@@ -13495,10 +13495,10 @@
         <v>31</v>
       </c>
       <c r="E451" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="F451" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G451" t="n">
         <v>151</v>
@@ -14220,10 +14220,10 @@
         <v>0</v>
       </c>
       <c r="E476" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F476" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G476" t="n">
         <v>8</v>
@@ -15873,13 +15873,13 @@
         <v>0</v>
       </c>
       <c r="E533" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F533" t="n">
         <v>13</v>
       </c>
       <c r="G533" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="534">
@@ -16105,13 +16105,13 @@
         <v>1</v>
       </c>
       <c r="E541" t="n">
-        <v>39.917</v>
+        <v>15.917</v>
       </c>
       <c r="F541" t="n">
         <v>7</v>
       </c>
       <c r="G541" t="n">
-        <v>47.917</v>
+        <v>23.917</v>
       </c>
     </row>
     <row r="542">
@@ -17065,10 +17065,10 @@
         <v>80</v>
       </c>
       <c r="F574" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G574" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="575">
@@ -20806,10 +20806,10 @@
         <v>1</v>
       </c>
       <c r="F703" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G703" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="704">
@@ -42408,13 +42408,13 @@
         <v>0</v>
       </c>
       <c r="E1448" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F1448" t="n">
         <v>32</v>
       </c>
       <c r="G1448" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1449">
@@ -42959,10 +42959,10 @@
         <v>0</v>
       </c>
       <c r="E1467" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1467" t="n">
         <v>6</v>
-      </c>
-      <c r="F1467" t="n">
-        <v>0</v>
       </c>
       <c r="G1467" t="n">
         <v>6</v>
@@ -46210,10 +46210,10 @@
         <v>60</v>
       </c>
       <c r="F1579" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G1579" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1580">
@@ -52329,10 +52329,10 @@
         <v>15</v>
       </c>
       <c r="F1790" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G1790" t="n">
-        <v>45.833</v>
+        <v>43.833</v>
       </c>
     </row>
     <row r="1791">
@@ -52935,13 +52935,13 @@
         <v>0</v>
       </c>
       <c r="E1811" t="n">
-        <v>5.417</v>
+        <v>2.417</v>
       </c>
       <c r="F1811" t="n">
         <v>0</v>
       </c>
       <c r="G1811" t="n">
-        <v>5.417</v>
+        <v>2.417</v>
       </c>
     </row>
     <row r="1812">
